--- a/sheets/대금율보/검수/남도굿거리.xlsx
+++ b/sheets/대금율보/검수/남도굿거리.xlsx
@@ -6643,32 +6643,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="119.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21"/>
       <c r="C3" s="22"/>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="119.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -6785,7 +6785,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="119.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -6821,7 +6821,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="119.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="24"/>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="119.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="119.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -6962,7 +6962,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="119.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="119.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="119.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="119.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="119.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="119.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -7269,10 +7269,10 @@
       <c r="T14" s="21"/>
       <c r="U14" s="24"/>
     </row>
-    <row r="15">
+    <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="80.0" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="119.22" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="119.22" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
       <c r="T18" s="21"/>
       <c r="U18" s="23"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="119.22" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="23"/>
@@ -7453,7 +7453,7 @@
       </c>
       <c r="U19" s="23"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="119.22" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
       <c r="T20" s="21"/>
       <c r="U20" s="24"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="119.22" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="119.22" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="23"/>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="U22" s="23"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="119.22" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="U23" s="23"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="119.22" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="U24" s="24"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="119.22" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="119.22" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
       <c r="T26" s="21"/>
       <c r="U26" s="23"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="119.22" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="119.22" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
       </c>
       <c r="U28" s="24"/>
     </row>
-    <row r="29">
+    <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="80.0" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="119.22" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="22"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="U31" s="22"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="119.22" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="23"/>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="U32" s="23"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="119.22" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="23"/>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="U33" s="23"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="119.22" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="24"/>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="U34" s="24"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="119.22" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="22"/>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="U35" s="22"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="119.22" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="23"/>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="U36" s="23"/>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="119.22" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21"/>
       <c r="C37" s="23"/>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="U37" s="23"/>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="119.22" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21"/>
       <c r="C38" s="24"/>
@@ -8204,7 +8204,7 @@
       <c r="T38" s="21"/>
       <c r="U38" s="24"/>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="119.22" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21"/>
       <c r="C39" s="22"/>
@@ -8227,7 +8227,7 @@
       <c r="T39" s="21"/>
       <c r="U39" s="22"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="119.22" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21"/>
       <c r="C40" s="23"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="U40" s="23"/>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="119.22" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21"/>
       <c r="C41" s="23"/>
@@ -8277,7 +8277,7 @@
       <c r="T41" s="21"/>
       <c r="U41" s="23"/>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="119.22" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21"/>
       <c r="C42" s="24"/>
@@ -8313,7 +8313,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
